--- a/artfynd/A 55229-2024 artfynd.xlsx
+++ b/artfynd/A 55229-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1303,6 +1303,136 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121416695</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98094</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>SV Råksjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>615219</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6658268</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Huddunge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2 m från snitslad gräns mellan nordlig avverkningsanmälan A 55229-2024 (4,5 ha schackrutehuggning) och sydlig avvanmälan   A 55274-2024 (13,3 ha överhållen skärm). Inga fältförsökskäppar.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55229-2024 artfynd.xlsx
+++ b/artfynd/A 55229-2024 artfynd.xlsx
@@ -1308,7 +1308,7 @@
         <v>121416695</v>
       </c>
       <c r="B8" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 55229-2024 artfynd.xlsx
+++ b/artfynd/A 55229-2024 artfynd.xlsx
@@ -1308,7 +1308,7 @@
         <v>121416695</v>
       </c>
       <c r="B8" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 55229-2024 artfynd.xlsx
+++ b/artfynd/A 55229-2024 artfynd.xlsx
@@ -1308,7 +1308,7 @@
         <v>121416695</v>
       </c>
       <c r="B8" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 55229-2024 artfynd.xlsx
+++ b/artfynd/A 55229-2024 artfynd.xlsx
@@ -1308,7 +1308,7 @@
         <v>121416695</v>
       </c>
       <c r="B8" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 55229-2024 artfynd.xlsx
+++ b/artfynd/A 55229-2024 artfynd.xlsx
@@ -1435,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121774874</v>
+        <v>121779195</v>
       </c>
       <c r="B9" t="n">
-        <v>78352</v>
+        <v>74661</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,44 +1447,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6426</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>SV Råksjön, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>615134</v>
+        <v>615226</v>
       </c>
       <c r="R9" t="n">
-        <v>6658383</v>
+        <v>6658305</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1513,7 +1510,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1523,12 +1520,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Kolad stubbe.</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1537,29 +1529,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121775186</v>
+        <v>121778952</v>
       </c>
       <c r="B10" t="n">
-        <v>97067</v>
+        <v>74661</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1572,37 +1563,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>6426</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>615376</v>
+        <v>615285</v>
       </c>
       <c r="R10" t="n">
-        <v>6658436</v>
+        <v>6658340</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1631,7 +1625,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1641,7 +1635,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På gran utanför den naturhänsynsnitslade kantzonen i anslutning till Flisbäcken.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1650,28 +1649,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121778952</v>
+        <v>121775186</v>
       </c>
       <c r="B11" t="n">
-        <v>74661</v>
+        <v>97067</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1684,40 +1684,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6426</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>615285</v>
+        <v>615376</v>
       </c>
       <c r="R11" t="n">
-        <v>6658340</v>
+        <v>6658436</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1746,7 +1743,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1756,12 +1753,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På gran utanför den naturhänsynsnitslade kantzonen i anslutning till Flisbäcken.</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,29 +1762,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121775464</v>
+        <v>121775206</v>
       </c>
       <c r="B12" t="n">
-        <v>90728</v>
+        <v>97067</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1801,25 +1792,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1829,13 +1820,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>615376</v>
+        <v>615375</v>
       </c>
       <c r="R12" t="n">
-        <v>6658373</v>
+        <v>6658434</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1864,7 +1855,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1874,7 +1865,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2013,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121779195</v>
+        <v>121774874</v>
       </c>
       <c r="B14" t="n">
-        <v>74661</v>
+        <v>78352</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2025,41 +2016,44 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>SV Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>615226</v>
+        <v>615134</v>
       </c>
       <c r="R14" t="n">
-        <v>6658305</v>
+        <v>6658383</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2088,7 +2082,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2098,7 +2092,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Kolad stubbe.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2107,28 +2106,29 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121775206</v>
+        <v>121775605</v>
       </c>
       <c r="B15" t="n">
-        <v>97067</v>
+        <v>90728</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2137,25 +2137,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2165,13 +2165,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615375</v>
+        <v>615359</v>
       </c>
       <c r="R15" t="n">
-        <v>6658434</v>
+        <v>6658381</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2237,7 +2237,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121775605</v>
+        <v>121775464</v>
       </c>
       <c r="B16" t="n">
         <v>90728</v>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615359</v>
+        <v>615376</v>
       </c>
       <c r="R16" t="n">
-        <v>6658381</v>
+        <v>6658373</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 55229-2024 artfynd.xlsx
+++ b/artfynd/A 55229-2024 artfynd.xlsx
@@ -1435,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121779195</v>
+        <v>121775760</v>
       </c>
       <c r="B9" t="n">
-        <v>74661</v>
+        <v>79657</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1451,37 +1451,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>SV Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>615226</v>
+        <v>615271</v>
       </c>
       <c r="R9" t="n">
-        <v>6658305</v>
+        <v>6658457</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1510,7 +1519,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1520,7 +1529,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Basen av asp ca 30 cm bhd.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1535,22 +1549,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121778952</v>
+        <v>121775597</v>
       </c>
       <c r="B10" t="n">
-        <v>74661</v>
+        <v>91168</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,44 +1573,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6426</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>615285</v>
+        <v>615359</v>
       </c>
       <c r="R10" t="n">
-        <v>6658340</v>
+        <v>6658381</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1625,7 +1636,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1635,12 +1646,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På gran utanför den naturhänsynsnitslade kantzonen i anslutning till Flisbäcken.</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1649,29 +1655,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121775186</v>
+        <v>121774874</v>
       </c>
       <c r="B11" t="n">
-        <v>97067</v>
+        <v>78352</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1680,41 +1685,44 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>SV Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>615376</v>
+        <v>615134</v>
       </c>
       <c r="R11" t="n">
-        <v>6658436</v>
+        <v>6658383</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1743,7 +1751,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1753,7 +1761,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Kolad stubbe.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1762,18 +1775,19 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1892,10 +1906,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121775597</v>
+        <v>121775605</v>
       </c>
       <c r="B13" t="n">
-        <v>91168</v>
+        <v>90728</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1904,25 +1918,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1967,7 +1981,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1977,7 +1991,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2004,10 +2018,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121774874</v>
+        <v>121775186</v>
       </c>
       <c r="B14" t="n">
-        <v>78352</v>
+        <v>97067</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2016,44 +2030,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>SV Råksjön, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>615134</v>
+        <v>615376</v>
       </c>
       <c r="R14" t="n">
-        <v>6658383</v>
+        <v>6658436</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2082,7 +2093,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2092,12 +2103,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Kolad stubbe.</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2106,26 +2112,25 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121775605</v>
+        <v>121775464</v>
       </c>
       <c r="B15" t="n">
         <v>90728</v>
@@ -2165,10 +2170,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615359</v>
+        <v>615376</v>
       </c>
       <c r="R15" t="n">
-        <v>6658381</v>
+        <v>6658373</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2200,7 +2205,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2210,7 +2215,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2237,10 +2242,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121775464</v>
+        <v>121779195</v>
       </c>
       <c r="B16" t="n">
-        <v>90728</v>
+        <v>74661</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2249,41 +2254,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615376</v>
+        <v>615226</v>
       </c>
       <c r="R16" t="n">
-        <v>6658373</v>
+        <v>6658305</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2312,7 +2317,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2322,7 +2327,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2337,22 +2342,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121775760</v>
+        <v>121778952</v>
       </c>
       <c r="B17" t="n">
-        <v>79657</v>
+        <v>74661</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2365,46 +2370,40 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229497</v>
+        <v>6426</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>SV Råksjön, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615271</v>
+        <v>615285</v>
       </c>
       <c r="R17" t="n">
-        <v>6658457</v>
+        <v>6658340</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2433,7 +2432,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2443,12 +2442,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Basen av asp ca 30 cm bhd.</t>
+          <t>På gran utanför den naturhänsynsnitslade kantzonen i anslutning till Flisbäcken.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2457,18 +2456,19 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 55229-2024 artfynd.xlsx
+++ b/artfynd/A 55229-2024 artfynd.xlsx
@@ -1435,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121775760</v>
+        <v>121775597</v>
       </c>
       <c r="B9" t="n">
-        <v>79657</v>
+        <v>91168</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,50 +1447,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229497</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>SV Råksjön, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>615271</v>
+        <v>615359</v>
       </c>
       <c r="R9" t="n">
-        <v>6658457</v>
+        <v>6658381</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1519,7 +1510,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1529,12 +1520,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:03</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Basen av asp ca 30 cm bhd.</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,22 +1535,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121775597</v>
+        <v>121775206</v>
       </c>
       <c r="B10" t="n">
-        <v>91168</v>
+        <v>97067</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1573,25 +1559,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,13 +1587,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>615359</v>
+        <v>615375</v>
       </c>
       <c r="R10" t="n">
-        <v>6658381</v>
+        <v>6658434</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1636,7 +1622,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1646,7 +1632,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,10 +1659,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121774874</v>
+        <v>121775605</v>
       </c>
       <c r="B11" t="n">
-        <v>78352</v>
+        <v>90728</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1689,40 +1675,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>SV Råksjön, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>615134</v>
+        <v>615359</v>
       </c>
       <c r="R11" t="n">
-        <v>6658383</v>
+        <v>6658381</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1751,7 +1734,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1761,12 +1744,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Kolad stubbe.</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1775,29 +1753,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121775206</v>
+        <v>121774874</v>
       </c>
       <c r="B12" t="n">
-        <v>97067</v>
+        <v>78352</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1806,41 +1783,44 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>SV Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>615375</v>
+        <v>615134</v>
       </c>
       <c r="R12" t="n">
-        <v>6658434</v>
+        <v>6658383</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1869,7 +1849,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1879,7 +1859,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Kolad stubbe.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1888,28 +1873,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121775605</v>
+        <v>121779195</v>
       </c>
       <c r="B13" t="n">
-        <v>90728</v>
+        <v>74661</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1918,41 +1904,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>615359</v>
+        <v>615226</v>
       </c>
       <c r="R13" t="n">
-        <v>6658381</v>
+        <v>6658305</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1981,7 +1967,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1991,7 +1977,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2006,12 +1992,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2130,10 +2116,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121775464</v>
+        <v>121775760</v>
       </c>
       <c r="B15" t="n">
-        <v>90728</v>
+        <v>79657</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2142,41 +2128,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>SV Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615376</v>
+        <v>615271</v>
       </c>
       <c r="R15" t="n">
-        <v>6658373</v>
+        <v>6658457</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2205,7 +2200,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2215,7 +2210,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Basen av asp ca 30 cm bhd.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2230,22 +2230,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121779195</v>
+        <v>121775464</v>
       </c>
       <c r="B16" t="n">
-        <v>74661</v>
+        <v>90728</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2254,41 +2254,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615226</v>
+        <v>615376</v>
       </c>
       <c r="R16" t="n">
-        <v>6658305</v>
+        <v>6658373</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2342,12 +2342,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 55229-2024 artfynd.xlsx
+++ b/artfynd/A 55229-2024 artfynd.xlsx
@@ -1435,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121775597</v>
+        <v>121775186</v>
       </c>
       <c r="B9" t="n">
-        <v>91168</v>
+        <v>97067</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,25 +1447,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1475,13 +1475,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>615359</v>
+        <v>615376</v>
       </c>
       <c r="R9" t="n">
-        <v>6658381</v>
+        <v>6658436</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1547,10 +1547,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121775206</v>
+        <v>121775597</v>
       </c>
       <c r="B10" t="n">
-        <v>97067</v>
+        <v>91168</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,25 +1559,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1587,13 +1587,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>615375</v>
+        <v>615359</v>
       </c>
       <c r="R10" t="n">
-        <v>6658434</v>
+        <v>6658381</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1659,10 +1659,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121775605</v>
+        <v>121779195</v>
       </c>
       <c r="B11" t="n">
-        <v>90728</v>
+        <v>74661</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1671,41 +1671,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>615359</v>
+        <v>615226</v>
       </c>
       <c r="R11" t="n">
-        <v>6658381</v>
+        <v>6658305</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,22 +1759,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121774874</v>
+        <v>121778952</v>
       </c>
       <c r="B12" t="n">
-        <v>78352</v>
+        <v>74661</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1783,25 +1783,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6426</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1810,17 +1810,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>SV Råksjön, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>615134</v>
+        <v>615285</v>
       </c>
       <c r="R12" t="n">
-        <v>6658383</v>
+        <v>6658340</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1859,12 +1859,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Kolad stubbe.</t>
+          <t>På gran utanför den naturhänsynsnitslade kantzonen i anslutning till Flisbäcken.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1880,22 +1880,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121779195</v>
+        <v>121775605</v>
       </c>
       <c r="B13" t="n">
-        <v>74661</v>
+        <v>90728</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1904,41 +1904,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>615226</v>
+        <v>615359</v>
       </c>
       <c r="R13" t="n">
-        <v>6658305</v>
+        <v>6658381</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1992,22 +1992,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121775186</v>
+        <v>121775760</v>
       </c>
       <c r="B14" t="n">
-        <v>97067</v>
+        <v>79657</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2020,34 +2020,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>229497</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>SV Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>615376</v>
+        <v>615271</v>
       </c>
       <c r="R14" t="n">
-        <v>6658436</v>
+        <v>6658457</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2079,7 +2088,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2089,7 +2098,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Basen av asp ca 30 cm bhd.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2104,22 +2118,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121775760</v>
+        <v>121775206</v>
       </c>
       <c r="B15" t="n">
-        <v>79657</v>
+        <v>97067</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2132,46 +2146,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229497</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>SV Råksjön, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615271</v>
+        <v>615375</v>
       </c>
       <c r="R15" t="n">
-        <v>6658457</v>
+        <v>6658434</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2200,7 +2205,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2210,12 +2215,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:03</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Basen av asp ca 30 cm bhd.</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2230,22 +2230,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121775464</v>
+        <v>121774874</v>
       </c>
       <c r="B16" t="n">
-        <v>90728</v>
+        <v>78352</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2258,37 +2258,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>SV Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615376</v>
+        <v>615134</v>
       </c>
       <c r="R16" t="n">
-        <v>6658373</v>
+        <v>6658383</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2317,7 +2320,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2327,7 +2330,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Kolad stubbe.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2336,28 +2344,29 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121778952</v>
+        <v>121775464</v>
       </c>
       <c r="B17" t="n">
-        <v>74661</v>
+        <v>90728</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2366,44 +2375,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615285</v>
+        <v>615376</v>
       </c>
       <c r="R17" t="n">
-        <v>6658340</v>
+        <v>6658373</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2432,7 +2438,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2442,12 +2448,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På gran utanför den naturhänsynsnitslade kantzonen i anslutning till Flisbäcken.</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2456,19 +2457,18 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 55229-2024 artfynd.xlsx
+++ b/artfynd/A 55229-2024 artfynd.xlsx
@@ -1435,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121775186</v>
+        <v>121775597</v>
       </c>
       <c r="B9" t="n">
-        <v>97067</v>
+        <v>91168</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,25 +1447,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1475,13 +1475,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>615376</v>
+        <v>615359</v>
       </c>
       <c r="R9" t="n">
-        <v>6658436</v>
+        <v>6658381</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1547,10 +1547,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121775597</v>
+        <v>121779195</v>
       </c>
       <c r="B10" t="n">
-        <v>91168</v>
+        <v>74661</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,41 +1559,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>6426</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>615359</v>
+        <v>615226</v>
       </c>
       <c r="R10" t="n">
-        <v>6658381</v>
+        <v>6658305</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1647,22 +1647,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121779195</v>
+        <v>121775760</v>
       </c>
       <c r="B11" t="n">
-        <v>74661</v>
+        <v>79657</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1675,37 +1675,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>SV Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>615226</v>
+        <v>615271</v>
       </c>
       <c r="R11" t="n">
-        <v>6658305</v>
+        <v>6658457</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1734,7 +1743,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1744,7 +1753,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Basen av asp ca 30 cm bhd.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,12 +1773,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1892,10 +1906,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121775605</v>
+        <v>121774874</v>
       </c>
       <c r="B13" t="n">
-        <v>90728</v>
+        <v>78352</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1908,37 +1922,40 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>SV Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>615359</v>
+        <v>615134</v>
       </c>
       <c r="R13" t="n">
-        <v>6658381</v>
+        <v>6658383</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1967,7 +1984,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1977,7 +1994,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Kolad stubbe.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1986,28 +2008,29 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121775760</v>
+        <v>121775464</v>
       </c>
       <c r="B14" t="n">
-        <v>79657</v>
+        <v>90728</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2016,50 +2039,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>SV Råksjön, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>615271</v>
+        <v>615376</v>
       </c>
       <c r="R14" t="n">
-        <v>6658457</v>
+        <v>6658373</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2088,7 +2102,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2098,12 +2112,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:03</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Basen av asp ca 30 cm bhd.</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2118,12 +2127,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2242,10 +2251,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121774874</v>
+        <v>121775186</v>
       </c>
       <c r="B16" t="n">
-        <v>78352</v>
+        <v>97067</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2254,44 +2263,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>SV Råksjön, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615134</v>
+        <v>615376</v>
       </c>
       <c r="R16" t="n">
-        <v>6658383</v>
+        <v>6658436</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2320,7 +2326,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2330,12 +2336,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Kolad stubbe.</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2344,26 +2345,25 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121775464</v>
+        <v>121775605</v>
       </c>
       <c r="B17" t="n">
         <v>90728</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615376</v>
+        <v>615359</v>
       </c>
       <c r="R17" t="n">
-        <v>6658373</v>
+        <v>6658381</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 55229-2024 artfynd.xlsx
+++ b/artfynd/A 55229-2024 artfynd.xlsx
@@ -1435,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121775597</v>
+        <v>121775186</v>
       </c>
       <c r="B9" t="n">
-        <v>91168</v>
+        <v>97067</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,25 +1447,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1475,13 +1475,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>615359</v>
+        <v>615376</v>
       </c>
       <c r="R9" t="n">
-        <v>6658381</v>
+        <v>6658436</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1547,10 +1547,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121779195</v>
+        <v>121775464</v>
       </c>
       <c r="B10" t="n">
-        <v>74661</v>
+        <v>90728</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,41 +1559,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>615226</v>
+        <v>615376</v>
       </c>
       <c r="R10" t="n">
-        <v>6658305</v>
+        <v>6658373</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1647,22 +1647,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121775760</v>
+        <v>121778952</v>
       </c>
       <c r="B11" t="n">
-        <v>79657</v>
+        <v>74661</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1675,46 +1675,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>6426</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>SV Råksjön, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>615271</v>
+        <v>615285</v>
       </c>
       <c r="R11" t="n">
-        <v>6658457</v>
+        <v>6658340</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1743,7 +1737,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1753,12 +1747,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Basen av asp ca 30 cm bhd.</t>
+          <t>På gran utanför den naturhänsynsnitslade kantzonen i anslutning till Flisbäcken.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1767,28 +1761,29 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121778952</v>
+        <v>121774874</v>
       </c>
       <c r="B12" t="n">
-        <v>74661</v>
+        <v>78352</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,25 +1792,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6426</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1824,17 +1819,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>SV Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>615285</v>
+        <v>615134</v>
       </c>
       <c r="R12" t="n">
-        <v>6658340</v>
+        <v>6658383</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1863,7 +1858,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1873,12 +1868,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gran utanför den naturhänsynsnitslade kantzonen i anslutning till Flisbäcken.</t>
+          <t>Kolad stubbe.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1894,22 +1889,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121774874</v>
+        <v>121775605</v>
       </c>
       <c r="B13" t="n">
-        <v>78352</v>
+        <v>90728</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1922,40 +1917,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>SV Råksjön, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>615134</v>
+        <v>615359</v>
       </c>
       <c r="R13" t="n">
-        <v>6658383</v>
+        <v>6658381</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1984,7 +1976,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1994,12 +1986,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Kolad stubbe.</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2008,29 +1995,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121775464</v>
+        <v>121775597</v>
       </c>
       <c r="B14" t="n">
-        <v>90728</v>
+        <v>91168</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2039,25 +2025,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2067,10 +2053,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>615376</v>
+        <v>615359</v>
       </c>
       <c r="R14" t="n">
-        <v>6658373</v>
+        <v>6658381</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2102,7 +2088,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2112,7 +2098,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2139,10 +2125,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121775206</v>
+        <v>121775760</v>
       </c>
       <c r="B15" t="n">
-        <v>97067</v>
+        <v>79657</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2155,37 +2141,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>229497</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>SV Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615375</v>
+        <v>615271</v>
       </c>
       <c r="R15" t="n">
-        <v>6658434</v>
+        <v>6658457</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2214,7 +2209,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2224,7 +2219,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Basen av asp ca 30 cm bhd.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2239,19 +2239,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121775186</v>
+        <v>121775206</v>
       </c>
       <c r="B16" t="n">
         <v>97067</v>
@@ -2291,13 +2291,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615376</v>
+        <v>615375</v>
       </c>
       <c r="R16" t="n">
-        <v>6658436</v>
+        <v>6658434</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2363,10 +2363,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121775605</v>
+        <v>121779195</v>
       </c>
       <c r="B17" t="n">
-        <v>90728</v>
+        <v>74661</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2375,41 +2375,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615359</v>
+        <v>615226</v>
       </c>
       <c r="R17" t="n">
-        <v>6658381</v>
+        <v>6658305</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2463,12 +2463,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 55229-2024 artfynd.xlsx
+++ b/artfynd/A 55229-2024 artfynd.xlsx
@@ -2251,10 +2251,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121775206</v>
+        <v>121779195</v>
       </c>
       <c r="B16" t="n">
-        <v>97067</v>
+        <v>74661</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2267,37 +2267,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>6426</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615375</v>
+        <v>615226</v>
       </c>
       <c r="R16" t="n">
-        <v>6658434</v>
+        <v>6658305</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2351,22 +2351,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121779195</v>
+        <v>121775206</v>
       </c>
       <c r="B17" t="n">
-        <v>74661</v>
+        <v>97067</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6426</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615226</v>
+        <v>615375</v>
       </c>
       <c r="R17" t="n">
-        <v>6658305</v>
+        <v>6658434</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2463,12 +2463,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 55229-2024 artfynd.xlsx
+++ b/artfynd/A 55229-2024 artfynd.xlsx
@@ -1435,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121775186</v>
+        <v>121775597</v>
       </c>
       <c r="B9" t="n">
-        <v>97067</v>
+        <v>91182</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,25 +1447,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1475,13 +1475,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>615376</v>
+        <v>615359</v>
       </c>
       <c r="R9" t="n">
-        <v>6658436</v>
+        <v>6658381</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1547,10 +1547,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121775464</v>
+        <v>121778952</v>
       </c>
       <c r="B10" t="n">
-        <v>90728</v>
+        <v>74674</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,41 +1559,44 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>615376</v>
+        <v>615285</v>
       </c>
       <c r="R10" t="n">
-        <v>6658373</v>
+        <v>6658340</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1622,7 +1625,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1632,7 +1635,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På gran utanför den naturhänsynsnitslade kantzonen i anslutning till Flisbäcken.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,28 +1649,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121778952</v>
+        <v>121774874</v>
       </c>
       <c r="B11" t="n">
-        <v>74661</v>
+        <v>78365</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1671,25 +1680,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6426</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1698,17 +1707,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>SV Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>615285</v>
+        <v>615134</v>
       </c>
       <c r="R11" t="n">
-        <v>6658340</v>
+        <v>6658383</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1737,7 +1746,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1747,12 +1756,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gran utanför den naturhänsynsnitslade kantzonen i anslutning till Flisbäcken.</t>
+          <t>Kolad stubbe.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,22 +1777,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121774874</v>
+        <v>121775464</v>
       </c>
       <c r="B12" t="n">
-        <v>78352</v>
+        <v>90742</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1796,40 +1805,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>SV Råksjön, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>615134</v>
+        <v>615376</v>
       </c>
       <c r="R12" t="n">
-        <v>6658383</v>
+        <v>6658373</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1858,7 +1864,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1868,12 +1874,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Kolad stubbe.</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,19 +1883,18 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1904,7 +1904,7 @@
         <v>121775605</v>
       </c>
       <c r="B13" t="n">
-        <v>90728</v>
+        <v>90742</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2013,10 +2013,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121775597</v>
+        <v>121779195</v>
       </c>
       <c r="B14" t="n">
-        <v>91168</v>
+        <v>74674</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2025,41 +2025,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>6426</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>615359</v>
+        <v>615226</v>
       </c>
       <c r="R14" t="n">
-        <v>6658381</v>
+        <v>6658305</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2113,12 +2113,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2128,7 +2128,7 @@
         <v>121775760</v>
       </c>
       <c r="B15" t="n">
-        <v>79657</v>
+        <v>79670</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2251,10 +2251,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121779195</v>
+        <v>121775186</v>
       </c>
       <c r="B16" t="n">
-        <v>74661</v>
+        <v>97085</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2267,37 +2267,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6426</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615226</v>
+        <v>615376</v>
       </c>
       <c r="R16" t="n">
-        <v>6658305</v>
+        <v>6658436</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2351,12 +2351,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2366,7 +2366,7 @@
         <v>121775206</v>
       </c>
       <c r="B17" t="n">
-        <v>97067</v>
+        <v>97085</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 55229-2024 artfynd.xlsx
+++ b/artfynd/A 55229-2024 artfynd.xlsx
@@ -1901,10 +1901,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121775605</v>
+        <v>121775760</v>
       </c>
       <c r="B13" t="n">
-        <v>90742</v>
+        <v>79670</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1913,41 +1913,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>SV Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>615359</v>
+        <v>615271</v>
       </c>
       <c r="R13" t="n">
-        <v>6658381</v>
+        <v>6658457</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1976,7 +1985,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1986,7 +1995,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Basen av asp ca 30 cm bhd.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2001,12 +2015,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2125,10 +2139,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121775760</v>
+        <v>121775605</v>
       </c>
       <c r="B15" t="n">
-        <v>79670</v>
+        <v>90742</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2137,50 +2151,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>SV Råksjön, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615271</v>
+        <v>615359</v>
       </c>
       <c r="R15" t="n">
-        <v>6658457</v>
+        <v>6658381</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2209,7 +2214,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2219,12 +2224,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:03</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Basen av asp ca 30 cm bhd.</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2239,12 +2239,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 55229-2024 artfynd.xlsx
+++ b/artfynd/A 55229-2024 artfynd.xlsx
@@ -1901,10 +1901,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121775760</v>
+        <v>121775605</v>
       </c>
       <c r="B13" t="n">
-        <v>79670</v>
+        <v>90742</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1913,50 +1913,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>SV Råksjön, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>615271</v>
+        <v>615359</v>
       </c>
       <c r="R13" t="n">
-        <v>6658457</v>
+        <v>6658381</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1985,7 +1976,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1995,12 +1986,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:03</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Basen av asp ca 30 cm bhd.</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2015,12 +2001,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2139,10 +2125,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121775605</v>
+        <v>121775760</v>
       </c>
       <c r="B15" t="n">
-        <v>90742</v>
+        <v>79670</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2151,41 +2137,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>SV Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615359</v>
+        <v>615271</v>
       </c>
       <c r="R15" t="n">
-        <v>6658381</v>
+        <v>6658457</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2214,7 +2209,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2224,7 +2219,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Basen av asp ca 30 cm bhd.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2239,12 +2239,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 55229-2024 artfynd.xlsx
+++ b/artfynd/A 55229-2024 artfynd.xlsx
@@ -1435,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121775597</v>
+        <v>121779195</v>
       </c>
       <c r="B9" t="n">
-        <v>91182</v>
+        <v>74676</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,41 +1447,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>6426</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>615359</v>
+        <v>615226</v>
       </c>
       <c r="R9" t="n">
-        <v>6658381</v>
+        <v>6658305</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1535,22 +1535,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121778952</v>
+        <v>121775597</v>
       </c>
       <c r="B10" t="n">
-        <v>74674</v>
+        <v>91184</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,44 +1559,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6426</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>615285</v>
+        <v>615359</v>
       </c>
       <c r="R10" t="n">
-        <v>6658340</v>
+        <v>6658381</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1625,7 +1622,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1635,12 +1632,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På gran utanför den naturhänsynsnitslade kantzonen i anslutning till Flisbäcken.</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1649,29 +1641,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121774874</v>
+        <v>121775605</v>
       </c>
       <c r="B11" t="n">
-        <v>78365</v>
+        <v>90744</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1684,40 +1675,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>SV Råksjön, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>615134</v>
+        <v>615359</v>
       </c>
       <c r="R11" t="n">
-        <v>6658383</v>
+        <v>6658381</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1746,7 +1734,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1756,12 +1744,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Kolad stubbe.</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,29 +1753,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121775464</v>
+        <v>121778952</v>
       </c>
       <c r="B12" t="n">
-        <v>90742</v>
+        <v>74676</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1801,41 +1783,44 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>615376</v>
+        <v>615285</v>
       </c>
       <c r="R12" t="n">
-        <v>6658373</v>
+        <v>6658340</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1864,7 +1849,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1874,7 +1859,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På gran utanför den naturhänsynsnitslade kantzonen i anslutning till Flisbäcken.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1883,28 +1873,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121775760</v>
+        <v>121775186</v>
       </c>
       <c r="B13" t="n">
-        <v>79670</v>
+        <v>97087</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1917,43 +1908,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229497</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>SV Råksjön, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>615271</v>
+        <v>615376</v>
       </c>
       <c r="R13" t="n">
-        <v>6658457</v>
+        <v>6658436</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1985,7 +1967,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1995,12 +1977,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:03</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Basen av asp ca 30 cm bhd.</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2015,22 +1992,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121779195</v>
+        <v>121774874</v>
       </c>
       <c r="B14" t="n">
-        <v>74674</v>
+        <v>78367</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2039,41 +2016,44 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>SV Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>615226</v>
+        <v>615134</v>
       </c>
       <c r="R14" t="n">
-        <v>6658305</v>
+        <v>6658383</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2102,7 +2082,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2112,7 +2092,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Kolad stubbe.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2121,28 +2106,29 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121775605</v>
+        <v>121775206</v>
       </c>
       <c r="B15" t="n">
-        <v>90742</v>
+        <v>97087</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2151,25 +2137,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2179,13 +2165,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615359</v>
+        <v>615375</v>
       </c>
       <c r="R15" t="n">
-        <v>6658381</v>
+        <v>6658434</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2214,7 +2200,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2224,7 +2210,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2251,10 +2237,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121775186</v>
+        <v>121775760</v>
       </c>
       <c r="B16" t="n">
-        <v>97085</v>
+        <v>79672</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2267,34 +2253,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>229497</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>SV Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615376</v>
+        <v>615271</v>
       </c>
       <c r="R16" t="n">
-        <v>6658436</v>
+        <v>6658457</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2326,7 +2321,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2336,7 +2331,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Basen av asp ca 30 cm bhd.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2351,22 +2351,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121775206</v>
+        <v>121775464</v>
       </c>
       <c r="B17" t="n">
-        <v>97085</v>
+        <v>90744</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2375,25 +2375,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2403,13 +2403,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615375</v>
+        <v>615376</v>
       </c>
       <c r="R17" t="n">
-        <v>6658434</v>
+        <v>6658373</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 55229-2024 artfynd.xlsx
+++ b/artfynd/A 55229-2024 artfynd.xlsx
@@ -1435,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121779195</v>
+        <v>121775597</v>
       </c>
       <c r="B9" t="n">
-        <v>74676</v>
+        <v>91185</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,41 +1447,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6426</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>615226</v>
+        <v>615359</v>
       </c>
       <c r="R9" t="n">
-        <v>6658305</v>
+        <v>6658381</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1535,22 +1535,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121775597</v>
+        <v>121779195</v>
       </c>
       <c r="B10" t="n">
-        <v>91184</v>
+        <v>74676</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,41 +1559,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>6426</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>615359</v>
+        <v>615226</v>
       </c>
       <c r="R10" t="n">
-        <v>6658381</v>
+        <v>6658305</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1647,22 +1647,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121775605</v>
+        <v>121775760</v>
       </c>
       <c r="B11" t="n">
-        <v>90744</v>
+        <v>79673</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1671,41 +1671,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>SV Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>615359</v>
+        <v>615271</v>
       </c>
       <c r="R11" t="n">
-        <v>6658381</v>
+        <v>6658457</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1734,7 +1743,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1744,7 +1753,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Basen av asp ca 30 cm bhd.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,22 +1773,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121778952</v>
+        <v>121775464</v>
       </c>
       <c r="B12" t="n">
-        <v>74676</v>
+        <v>90745</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1783,44 +1797,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>615285</v>
+        <v>615376</v>
       </c>
       <c r="R12" t="n">
-        <v>6658340</v>
+        <v>6658373</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1849,7 +1860,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1859,12 +1870,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På gran utanför den naturhänsynsnitslade kantzonen i anslutning till Flisbäcken.</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1873,19 +1879,18 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1895,7 +1900,7 @@
         <v>121775186</v>
       </c>
       <c r="B13" t="n">
-        <v>97087</v>
+        <v>97094</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2007,7 +2012,7 @@
         <v>121774874</v>
       </c>
       <c r="B14" t="n">
-        <v>78367</v>
+        <v>78368</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2125,10 +2130,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121775206</v>
+        <v>121778952</v>
       </c>
       <c r="B15" t="n">
-        <v>97087</v>
+        <v>74676</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2141,37 +2146,40 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>6426</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615375</v>
+        <v>615285</v>
       </c>
       <c r="R15" t="n">
-        <v>6658434</v>
+        <v>6658340</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2200,7 +2208,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2210,7 +2218,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På gran utanför den naturhänsynsnitslade kantzonen i anslutning till Flisbäcken.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2219,28 +2232,29 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121775760</v>
+        <v>121775605</v>
       </c>
       <c r="B16" t="n">
-        <v>79672</v>
+        <v>90745</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2249,50 +2263,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>SV Råksjön, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615271</v>
+        <v>615359</v>
       </c>
       <c r="R16" t="n">
-        <v>6658457</v>
+        <v>6658381</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2321,7 +2326,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2331,12 +2336,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:03</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Basen av asp ca 30 cm bhd.</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2351,22 +2351,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121775464</v>
+        <v>121775206</v>
       </c>
       <c r="B17" t="n">
-        <v>90744</v>
+        <v>97094</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2375,25 +2375,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2403,13 +2403,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615376</v>
+        <v>615375</v>
       </c>
       <c r="R17" t="n">
-        <v>6658373</v>
+        <v>6658434</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 55229-2024 artfynd.xlsx
+++ b/artfynd/A 55229-2024 artfynd.xlsx
@@ -1547,10 +1547,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121779195</v>
+        <v>121775760</v>
       </c>
       <c r="B10" t="n">
-        <v>74676</v>
+        <v>79673</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1563,37 +1563,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>SV Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>615226</v>
+        <v>615271</v>
       </c>
       <c r="R10" t="n">
-        <v>6658305</v>
+        <v>6658457</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1622,7 +1631,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1632,7 +1641,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Basen av asp ca 30 cm bhd.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1647,22 +1661,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121775760</v>
+        <v>121779195</v>
       </c>
       <c r="B11" t="n">
-        <v>79673</v>
+        <v>74676</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1675,46 +1689,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>6426</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>SV Råksjön, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>615271</v>
+        <v>615226</v>
       </c>
       <c r="R11" t="n">
-        <v>6658457</v>
+        <v>6658305</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1743,7 +1748,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1753,12 +1758,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:03</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Basen av asp ca 30 cm bhd.</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1773,12 +1773,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 55229-2024 artfynd.xlsx
+++ b/artfynd/A 55229-2024 artfynd.xlsx
@@ -1435,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121775597</v>
+        <v>121775464</v>
       </c>
       <c r="B9" t="n">
-        <v>91185</v>
+        <v>90754</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,25 +1447,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>615359</v>
+        <v>615376</v>
       </c>
       <c r="R9" t="n">
-        <v>6658381</v>
+        <v>6658373</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1547,10 +1547,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121775760</v>
+        <v>121775605</v>
       </c>
       <c r="B10" t="n">
-        <v>79673</v>
+        <v>90754</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,50 +1559,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>SV Råksjön, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>615271</v>
+        <v>615359</v>
       </c>
       <c r="R10" t="n">
-        <v>6658457</v>
+        <v>6658381</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1631,7 +1622,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1641,12 +1632,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:03</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Basen av asp ca 30 cm bhd.</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1661,22 +1647,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121779195</v>
+        <v>121775186</v>
       </c>
       <c r="B11" t="n">
-        <v>74676</v>
+        <v>97103</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1689,37 +1675,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6426</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Flisbäcken, söder om, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>615226</v>
+        <v>615376</v>
       </c>
       <c r="R11" t="n">
-        <v>6658305</v>
+        <v>6658436</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1748,7 +1734,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1758,7 +1744,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1773,22 +1759,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121775464</v>
+        <v>121775597</v>
       </c>
       <c r="B12" t="n">
-        <v>90745</v>
+        <v>91194</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,25 +1783,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1825,10 +1811,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>615376</v>
+        <v>615359</v>
       </c>
       <c r="R12" t="n">
-        <v>6658373</v>
+        <v>6658381</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1860,7 +1846,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1870,7 +1856,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1897,10 +1883,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121775186</v>
+        <v>121774874</v>
       </c>
       <c r="B13" t="n">
-        <v>97094</v>
+        <v>78375</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1909,41 +1895,44 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>SV Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>615376</v>
+        <v>615134</v>
       </c>
       <c r="R13" t="n">
-        <v>6658436</v>
+        <v>6658383</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1972,7 +1961,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,7 +1971,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Kolad stubbe.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1991,28 +1985,29 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121774874</v>
+        <v>121775206</v>
       </c>
       <c r="B14" t="n">
-        <v>78368</v>
+        <v>97103</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2021,44 +2016,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>SV Råksjön, Upl</t>
+          <t>Flisbäcken, Flisbäcken, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>615134</v>
+        <v>615375</v>
       </c>
       <c r="R14" t="n">
-        <v>6658383</v>
+        <v>6658434</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2087,7 +2079,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2097,12 +2089,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Kolad stubbe.</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2111,29 +2098,28 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121778952</v>
+        <v>121779195</v>
       </c>
       <c r="B15" t="n">
-        <v>74676</v>
+        <v>74680</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2164,19 +2150,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615285</v>
+        <v>615226</v>
       </c>
       <c r="R15" t="n">
-        <v>6658340</v>
+        <v>6658305</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2208,7 +2191,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2218,12 +2201,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På gran utanför den naturhänsynsnitslade kantzonen i anslutning till Flisbäcken.</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2232,7 +2210,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2251,10 +2228,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121775605</v>
+        <v>121778952</v>
       </c>
       <c r="B16" t="n">
-        <v>90745</v>
+        <v>74680</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2263,41 +2240,44 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>Flisbäcken, söder om, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>615359</v>
+        <v>615285</v>
       </c>
       <c r="R16" t="n">
-        <v>6658381</v>
+        <v>6658340</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2326,7 +2306,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2336,7 +2316,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På gran utanför den naturhänsynsnitslade kantzonen i anslutning till Flisbäcken.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2345,28 +2330,29 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121775206</v>
+        <v>121775760</v>
       </c>
       <c r="B17" t="n">
-        <v>97094</v>
+        <v>79680</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2379,37 +2365,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>229497</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Flisbäcken, Flisbäcken, Upl</t>
+          <t>SV Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615375</v>
+        <v>615271</v>
       </c>
       <c r="R17" t="n">
-        <v>6658434</v>
+        <v>6658457</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2438,7 +2433,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2448,7 +2443,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Basen av asp ca 30 cm bhd.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2463,12 +2463,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 55229-2024 artfynd.xlsx
+++ b/artfynd/A 55229-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2575,6 +2575,103 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>125855811</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97202</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Råksjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>615266</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6658456</v>
+      </c>
+      <c r="S19" t="n">
+        <v>12</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Huddunge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55229-2024 artfynd.xlsx
+++ b/artfynd/A 55229-2024 artfynd.xlsx
@@ -2580,7 +2580,7 @@
         <v>125855811</v>
       </c>
       <c r="B19" t="n">
-        <v>97202</v>
+        <v>97209</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 55229-2024 artfynd.xlsx
+++ b/artfynd/A 55229-2024 artfynd.xlsx
@@ -2580,7 +2580,7 @@
         <v>125855811</v>
       </c>
       <c r="B19" t="n">
-        <v>97209</v>
+        <v>97210</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 55229-2024 artfynd.xlsx
+++ b/artfynd/A 55229-2024 artfynd.xlsx
@@ -2580,7 +2580,7 @@
         <v>125855811</v>
       </c>
       <c r="B19" t="n">
-        <v>97210</v>
+        <v>97212</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 55229-2024 artfynd.xlsx
+++ b/artfynd/A 55229-2024 artfynd.xlsx
@@ -2580,7 +2580,7 @@
         <v>125855811</v>
       </c>
       <c r="B19" t="n">
-        <v>97212</v>
+        <v>97216</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 55229-2024 artfynd.xlsx
+++ b/artfynd/A 55229-2024 artfynd.xlsx
@@ -2580,7 +2580,7 @@
         <v>125855811</v>
       </c>
       <c r="B19" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 55229-2024 artfynd.xlsx
+++ b/artfynd/A 55229-2024 artfynd.xlsx
@@ -2580,7 +2580,7 @@
         <v>125855811</v>
       </c>
       <c r="B19" t="n">
-        <v>97217</v>
+        <v>97219</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 55229-2024 artfynd.xlsx
+++ b/artfynd/A 55229-2024 artfynd.xlsx
@@ -2580,7 +2580,7 @@
         <v>125855811</v>
       </c>
       <c r="B19" t="n">
-        <v>97219</v>
+        <v>97221</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 55229-2024 artfynd.xlsx
+++ b/artfynd/A 55229-2024 artfynd.xlsx
@@ -2580,7 +2580,7 @@
         <v>125855811</v>
       </c>
       <c r="B19" t="n">
-        <v>97221</v>
+        <v>97223</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 55229-2024 artfynd.xlsx
+++ b/artfynd/A 55229-2024 artfynd.xlsx
@@ -2580,7 +2580,7 @@
         <v>125855811</v>
       </c>
       <c r="B19" t="n">
-        <v>97223</v>
+        <v>97227</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 55229-2024 artfynd.xlsx
+++ b/artfynd/A 55229-2024 artfynd.xlsx
@@ -2580,7 +2580,7 @@
         <v>125855811</v>
       </c>
       <c r="B19" t="n">
-        <v>97227</v>
+        <v>97230</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 55229-2024 artfynd.xlsx
+++ b/artfynd/A 55229-2024 artfynd.xlsx
@@ -2580,7 +2580,7 @@
         <v>125855811</v>
       </c>
       <c r="B19" t="n">
-        <v>97230</v>
+        <v>97239</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
